--- a/runs/RELX/2026-10-14/bear/scratch/g_rf_bbg/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_rf_bbg/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2049.824275944262</v>
+        <v>2107.949574570711</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.102545</v>
+        <v>0.09476180000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.095427138964</v>
+        <v>0.08864158954000001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11148.0621727555</v>
+        <v>11317.40002423226</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>38172.88530124984</v>
+        <v>41946.45758598504</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>25329.65380870891</v>
+        <v>28622.86765163275</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36477.71598146441</v>
+        <v>39940.26767586501</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>29480.71598146441</v>
+        <v>32943.26767586501</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>28551.04362637668</v>
+        <v>32091.98776720374</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.37331396686541</v>
+        <v>18.40395743179754</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1637.331396686541</v>
+        <v>1840.395743179754</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4091189474</v>
+        <v>-0.3358369747</v>
       </c>
     </row>
   </sheetData>
